--- a/data/trans_dic/IP12B$cabeza-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,75; 81,24</t>
+          <t>12,26; 88,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,0</t>
+          <t>0,0; 45,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,87</t>
+          <t>0,0; 34,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,85</t>
+          <t>0,0; 56,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,54</t>
+          <t>0,0; 40,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,21</t>
+          <t>0,0; 19,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,23; 54,72</t>
+          <t>11,74; 58,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,01</t>
+          <t>0,0; 31,43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,63</t>
+          <t>0,0; 31,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,06</t>
+          <t>0,0; 27,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,97</t>
+          <t>0,0; 19,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,39</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,8</t>
+          <t>0,0; 49,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,08</t>
+          <t>0,0; 23,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,67</t>
+          <t>0,0; 48,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,02</t>
+          <t>0,0; 35,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,55</t>
+          <t>0,0; 41,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,52</t>
+          <t>0,0; 31,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,28</t>
+          <t>0,0; 19,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,71</t>
+          <t>0,0; 22,95</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,69</t>
+          <t>0,0; 39,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,21</t>
+          <t>0,0; 60,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,79</t>
+          <t>0,0; 24,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,98</t>
+          <t>0,0; 38,68</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,08</t>
+          <t>0,0; 20,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,25</t>
+          <t>0,0; 18,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,69</t>
+          <t>1,44; 13,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 12,7</t>
+          <t>2,16; 12,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 12,26</t>
+          <t>1,17; 13,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,39</t>
+          <t>1,1; 11,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,04</t>
+          <t>0,0; 12,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 9,32</t>
+          <t>1,42; 7,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 9,07</t>
+          <t>2,21; 9,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,06</t>
+          <t>1,37; 8,93</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3973</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>606; 4361</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4200</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2730</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4627</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4102</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2687</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1546; 7661</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6066</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3292</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3330</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3217</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3313</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3593</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3588</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3137</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3067</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3998</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4588</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2886</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4481</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2995</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3605</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2889</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4177</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2779</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3733</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2158</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2531</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3475</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>631; 5838</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1321; 7408</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>645; 7630</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4515</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>699; 7449</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0; 6036</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1283; 7126</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2760; 11640</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1413; 9195</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$cabeza-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,42 +683,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,26; 88,19</t>
+          <t>13,16; 82,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,82</t>
+          <t>0,0; 44,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,59</t>
+          <t>0,0; 34,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,24</t>
+          <t>0,0; 53,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,47</t>
+          <t>0,0; 38,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,73</t>
+          <t>0,0; 22,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,74; 58,16</t>
+          <t>11,68; 56,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,43</t>
+          <t>0,0; 28,65</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,94</t>
+          <t>0,0; 30,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,44</t>
+          <t>0,0; 26,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,94</t>
+          <t>0,0; 19,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,72</t>
+          <t>0,0; 10,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,35</t>
+          <t>0,0; 39,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,45</t>
+          <t>0,0; 22,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,63</t>
+          <t>0,0; 54,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,93</t>
+          <t>0,0; 36,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,3</t>
+          <t>0,0; 45,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,38</t>
+          <t>0,0; 26,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,39</t>
+          <t>0,0; 22,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,95</t>
+          <t>0,0; 19,42</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,55</t>
+          <t>0,0; 45,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,57</t>
+          <t>0,0; 58,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,88</t>
+          <t>0,0; 25,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,68</t>
+          <t>0,0; 38,07</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,0</t>
+          <t>0,0; 20,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,95</t>
+          <t>0,0; 18,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,31</t>
+          <t>1,42; 13,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,09</t>
+          <t>2,18; 13,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 13,84</t>
+          <t>1,15; 11,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 10,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,72</t>
+          <t>1,1; 11,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,61</t>
+          <t>0,0; 11,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,87</t>
+          <t>1,42; 8,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,32</t>
+          <t>2,18; 8,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,93</t>
+          <t>1,65; 9,34</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1866,42 +1866,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>606; 4361</t>
+          <t>651; 4077</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4200</t>
+          <t>0; 4059</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2730</t>
+          <t>0; 2688</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4627</t>
+          <t>0; 4387</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4102</t>
+          <t>0; 3880</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2687</t>
+          <t>0; 3103</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1546; 7661</t>
+          <t>1539; 7450</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6066</t>
+          <t>0; 5530</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3292</t>
+          <t>0; 3134</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3330</t>
+          <t>0; 3255</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3217</t>
+          <t>0; 3071</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3313</t>
+          <t>0; 2717</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3593</t>
+          <t>0; 2911</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3588</t>
+          <t>0; 3450</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3137</t>
+          <t>0; 3514</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3067</t>
+          <t>0; 3099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2375,22 +2375,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>0; 4422</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4588</t>
+          <t>0; 3877</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2886</t>
+          <t>0; 3339</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4481</t>
+          <t>0; 3792</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2995</t>
+          <t>0; 3408</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3605</t>
+          <t>0; 3511</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2889</t>
+          <t>0; 2953</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4177</t>
+          <t>0; 4111</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2779</t>
+          <t>0; 2784</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3733</t>
+          <t>0; 3712</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>631; 5838</t>
+          <t>625; 5714</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1321; 7408</t>
+          <t>1339; 7993</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>645; 7630</t>
+          <t>632; 6543</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0; 4515</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>699; 7449</t>
+          <t>697; 7349</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 6036</t>
+          <t>0; 5371</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1283; 7126</t>
+          <t>1285; 7474</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2760; 11640</t>
+          <t>2718; 10619</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1413; 9195</t>
+          <t>1699; 9614</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$cabeza-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>21,65%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>44,32%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,36%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 50,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,16; 82,44</t>
+          <t>0,0; 56,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,28</t>
+          <t>0,0; 37,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,33</t>
+          <t>12,75; 81,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,28</t>
+          <t>0,0; 51,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,79</t>
+          <t>0,0; 21,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,68; 56,56</t>
+          <t>11,23; 54,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,65</t>
+          <t>0,0; 33,01</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,13%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,41%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 22,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,04</t>
+          <t>0,0; 19,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,0; 13,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 39,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,55</t>
+          <t>0,0; 27,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>12,49%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 48,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,51</t>
+          <t>0,0; 27,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,43</t>
+          <t>0,0; 23,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,42</t>
+          <t>0,0; 24,71</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9,51%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>23,49%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 60,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,43</t>
+          <t>0,0; 30,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,07</t>
+          <t>0,0; 38,98</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,85</t>
+          <t>0,0; 19,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,92%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4,59%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,02</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,04</t>
+          <t>1,09; 10,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,87</t>
+          <t>0,0; 13,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>1,46; 12,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,56</t>
+          <t>2,17; 12,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,22</t>
+          <t>1,14; 12,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,25</t>
+          <t>1,44; 9,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,51</t>
+          <t>1,87; 9,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,34</t>
+          <t>1,54; 9,06</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,27 +1755,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>638</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2192</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1133</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1781</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4015</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>651; 4077</t>
+          <t>0; 4677</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4059</t>
+          <t>0; 3805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2688</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4387</t>
+          <t>631; 4017</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3880</t>
+          <t>0; 4675</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3103</t>
+          <t>0; 2888</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1539; 7450</t>
+          <t>1479; 7207</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5530</t>
+          <t>0; 6372</t>
         </is>
       </c>
     </row>
@@ -1918,27 +1918,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1971,27 +1971,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>656</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3134</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3255</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3157</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2678</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3071</t>
+          <t>0; 3221</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2717</t>
+          <t>0; 3486</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2897</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2911</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3450</t>
+          <t>0; 4143</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3514</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3099</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4023</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3139</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3417</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4422</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3877</t>
+          <t>0; 4024</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3339</t>
+          <t>0; 3466</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3792</t>
+          <t>0; 4825</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>720</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1398</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3408</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3511</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3583</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2953</t>
+          <t>0; 3577</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 4209</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>680</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4040</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2784</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3712</t>
+          <t>0; 3791</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>2158</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>3517</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>2531</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2472</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1809</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>625; 5714</t>
+          <t>0; 4153</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1339; 7993</t>
+          <t>690; 6601</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>632; 6543</t>
+          <t>0; 6241</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>639; 5567</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>697; 7349</t>
+          <t>1329; 7782</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 5371</t>
+          <t>627; 6756</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1285; 7474</t>
+          <t>1304; 8444</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2718; 10619</t>
+          <t>2335; 11319</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1699; 9614</t>
+          <t>1581; 9329</t>
         </is>
       </c>
     </row>
